--- a/wiki/reports/daily/2026-10-12_일일보고.xlsx
+++ b/wiki/reports/daily/2026-10-12_일일보고.xlsx
@@ -613,7 +613,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성: 2026-10-12 07:56   |   전일: 10월 8일   |   월평균 기준: 이전 작업일 5일 평균   |   10월 누적 작업일: 6일</t>
+          <t>생성: 2026-10-12 07:57   |   전일: 10월 8일   |   월평균 기준: 이전 작업일 5일 평균   |   10월 누적 작업일: 6일</t>
         </is>
       </c>
     </row>

--- a/wiki/reports/daily/2026-10-12_일일보고.xlsx
+++ b/wiki/reports/daily/2026-10-12_일일보고.xlsx
@@ -76,7 +76,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -95,12 +95,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FADBD8"/>
+        <fgColor rgb="00D5F5E3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FADBD8"/>
       </patternFill>
     </fill>
     <fill>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -185,19 +190,25 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -209,10 +220,10 @@
     <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -613,7 +624,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성: 2026-10-12 07:57   |   전일: 10월 8일   |   월평균 기준: 이전 작업일 5일 평균   |   10월 누적 작업일: 6일</t>
+          <t>생성: 2026-10-12 16:00   |   전일: 10월 8일   |   월평균 기준: 이전 작업일 5일 평균   |   10월 누적 작업일: 6일</t>
         </is>
       </c>
     </row>
@@ -675,25 +686,25 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>42</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>-39</v>
+        <v>30</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-0.9285714285714286</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>48.8</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>-45.8</v>
+        <v>23.2</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>-0.9385245901639344</v>
+        <v>0.4754098360655739</v>
       </c>
       <c r="I4" s="10" t="inlineStr"/>
     </row>
@@ -704,29 +715,29 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>930</v>
+        <v>15744</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>8014</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-7084</v>
+        <v>7730</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-0.883953082106314</v>
+        <v>0.9645620164711755</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>11902</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-10972</v>
+        <v>3842</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>-0.9218618719542934</v>
+        <v>0.3228028902705428</v>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>0:15:30</t>
+          <t>4:22:24</t>
         </is>
       </c>
     </row>
@@ -742,19 +753,19 @@
       <c r="C6" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="12" t="n">
         <v>-34</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="13" t="n">
         <v>-0.9714285714285714</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>39.4</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="G6" s="12" t="n">
         <v>-38.4</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="H6" s="13" t="n">
         <v>-0.9746192893401016</v>
       </c>
       <c r="I6" s="10" t="inlineStr"/>
@@ -771,19 +782,19 @@
       <c r="C7" s="6" t="n">
         <v>9035</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="12" t="n">
         <v>-9034</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="13" t="n">
         <v>-0.9998893193137798</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>11714.8</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="G7" s="12" t="n">
         <v>-11713.8</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="13" t="n">
         <v>-0.9999146378939461</v>
       </c>
       <c r="I7" s="10" t="inlineStr">
@@ -793,116 +804,116 @@
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>합계  수량 (개)</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>77</v>
       </c>
-      <c r="D8" s="7" t="n">
-        <v>-73</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>-0.948051948051948</v>
+      <c r="D8" s="12" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>-0.05194805194805195</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>88.2</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>-84.2</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>-0.9546485260770975</v>
+      <c r="G8" s="12" t="n">
+        <v>-15.2</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>-0.1723356009070295</v>
       </c>
       <c r="I8" s="10" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>합계  가공시간 (초)</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>931</v>
+        <v>15745</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>17049</v>
       </c>
-      <c r="D9" s="7" t="n">
-        <v>-16118</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>-0.9453926916534694</v>
+      <c r="D9" s="12" t="n">
+        <v>-1304</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>-0.0764854243650654</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>23616.8</v>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>-22685.8</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>-0.9605789099285255</v>
+      <c r="G9" s="12" t="n">
+        <v>-7871.799999999999</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>-0.3333135733884353</v>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>0:15:31</t>
+          <t>4:22:25</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>합계  금액</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>77</v>
       </c>
-      <c r="D10" s="7" t="n">
-        <v>-73</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>-0.948051948051948</v>
+      <c r="D10" s="12" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>-0.05194805194805195</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>88.2</v>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>-84.2</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>-0.9546485260770975</v>
+      <c r="G10" s="12" t="n">
+        <v>-15.2</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>-0.1723356009070295</v>
       </c>
       <c r="I10" s="10" t="inlineStr"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>10월 누적  (6일 / 12일 중 작업일)</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="14" t="n">
-        <v>445</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>119015</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>445</v>
-      </c>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="13" t="n"/>
-      <c r="I11" s="13" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="16" t="n">
+        <v>514</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>133829</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>514</v>
+      </c>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="15" t="n"/>
+      <c r="I11" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -920,7 +931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -944,260 +955,465 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>■ FAST GRIND</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>형상</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>날수(F)</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>날경(Ø)</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>상크경(Ø)</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>코팅</t>
         </is>
       </c>
-      <c r="G3" s="16" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>특이사항</t>
         </is>
       </c>
-      <c r="H3" s="16" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I3" s="16" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>수량(개)</t>
         </is>
       </c>
-      <c r="J3" s="16" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>시간합계(초)</t>
         </is>
       </c>
-      <c r="K3" s="16" t="inlineStr">
+      <c r="K3" s="18" t="inlineStr">
         <is>
           <t>시간(H:M:S)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="17" t="n">
+      <c r="A4" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>볼</t>
         </is>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>뮤</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
-        <is>
-          <t>0153</t>
-        </is>
-      </c>
-      <c r="H4" s="17" t="inlineStr"/>
-      <c r="I4" s="19" t="n">
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>0153, 0155</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr"/>
+      <c r="I4" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" s="21" t="n">
+        <v>1240</v>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>0:20:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>R1.2</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>0243</t>
+        </is>
+      </c>
+      <c r="H5" s="19" t="inlineStr"/>
+      <c r="I5" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="J5" s="21" t="n">
+        <v>4320</v>
+      </c>
+      <c r="K5" s="19" t="inlineStr">
+        <is>
+          <t>1:12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="19" t="n">
-        <v>930</v>
-      </c>
-      <c r="K4" s="17" t="inlineStr">
-        <is>
-          <t>0:15:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>면취</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>0106</t>
+        </is>
+      </c>
+      <c r="H6" s="19" t="inlineStr"/>
+      <c r="I6" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" s="21" t="n">
+        <v>1584</v>
+      </c>
+      <c r="K6" s="19" t="inlineStr">
+        <is>
+          <t>0:26:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>0106</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr"/>
+      <c r="I7" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="21" t="n">
+        <v>840</v>
+      </c>
+      <c r="K7" s="19" t="inlineStr">
+        <is>
+          <t>0:14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>평_라핑</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="H8" s="19" t="inlineStr"/>
+      <c r="I8" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="21" t="n">
+        <v>360</v>
+      </c>
+      <c r="K8" s="19" t="inlineStr">
+        <is>
+          <t>0:06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>0040</t>
+        </is>
+      </c>
+      <c r="H9" s="19" t="inlineStr"/>
+      <c r="I9" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="J9" s="21" t="n">
+        <v>7400</v>
+      </c>
+      <c r="K9" s="19" t="inlineStr">
+        <is>
+          <t>2:03:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>FAST GRIND 소계</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="J5" s="14" t="n">
-        <v>930</v>
-      </c>
-      <c r="K5" s="13" t="inlineStr">
-        <is>
-          <t>0:15:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="15" t="n"/>
+      <c r="I10" s="16" t="n">
+        <v>72</v>
+      </c>
+      <c r="J10" s="16" t="n">
+        <v>15744</v>
+      </c>
+      <c r="K10" s="15" t="inlineStr">
+        <is>
+          <t>4:22:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>■ GX7</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>형상</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>날수(F)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>날경(Ø)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>상크경(Ø)</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>코팅</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>특이사항</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t>수량(개)</t>
         </is>
       </c>
-      <c r="J8" s="21" t="inlineStr">
+      <c r="J13" s="23" t="inlineStr">
         <is>
           <t>시간합계(초)</t>
         </is>
       </c>
-      <c r="K8" s="21" t="inlineStr">
+      <c r="K13" s="23" t="inlineStr">
         <is>
           <t>시간(H:M:S)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="22" t="n">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>드릴</t>
         </is>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C14" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D14" s="24" t="n">
         <v>3.4</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E14" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t>뮤</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>0168</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr"/>
-      <c r="I9" s="24" t="n">
+      <c r="H14" s="24" t="inlineStr"/>
+      <c r="I14" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="24" t="n">
+      <c r="J14" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K14" s="24" t="inlineStr">
         <is>
           <t>0:00:01</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>GX7 소계</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="13" t="n"/>
-      <c r="I10" s="14" t="n">
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="15" t="n"/>
+      <c r="G15" s="15" t="n"/>
+      <c r="H15" s="15" t="n"/>
+      <c r="I15" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="14" t="n">
+      <c r="J15" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="K10" s="13" t="inlineStr">
+      <c r="K15" s="15" t="inlineStr">
         <is>
           <t>0:00:01</t>
         </is>
@@ -1205,10 +1421,10 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A15:H15"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
